--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488212_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488212_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4451</v>
+        <v>8.779299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0259</v>
+        <v>6.5817</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4192</v>
+        <v>2.1976</v>
       </c>
       <c r="G2" t="n">
         <v>4.4015</v>
@@ -610,13 +610,13 @@
         <v>3.3352</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8583</v>
+        <v>1.1925</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5296999999999999</v>
+        <v>0.0261</v>
       </c>
       <c r="U2" t="n">
-        <v>1.388</v>
+        <v>1.1664</v>
       </c>
       <c r="V2" t="n">
         <v>1.8883</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>T. PERRY II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.153499999999999</v>
+        <v>8.142799999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0089</v>
+        <v>6.5435</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1447</v>
+        <v>1.5993</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9082</v>
+        <v>-0.3802</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0112</v>
+        <v>-0.744</v>
       </c>
       <c r="I3" t="n">
-        <v>1.897</v>
+        <v>0.3638</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5258</v>
+        <v>0.9739</v>
       </c>
       <c r="K3" t="n">
-        <v>4.105</v>
+        <v>0.9099</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4207</v>
+        <v>0.0641</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6175</v>
+        <v>-1.3541</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0938</v>
+        <v>-1.6538</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4763</v>
+        <v>0.2997</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2234</v>
+        <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2279</v>
+        <v>1.3023</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4303</v>
+        <v>0.2018</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7976</v>
+        <v>1.1005</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5733</v>
+        <v>6.2943</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8321</v>
+        <v>6.2943</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. PERRY II</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.2964</v>
+        <v>6.7781</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1403</v>
+        <v>5.4213</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1561</v>
+        <v>1.3568</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3802</v>
+        <v>4.9082</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.744</v>
+        <v>3.0112</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3638</v>
+        <v>1.897</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9739</v>
+        <v>5.5258</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9099</v>
+        <v>4.105</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0641</v>
+        <v>1.4207</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3541</v>
+        <v>-0.6175</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6538</v>
+        <v>-1.0938</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2997</v>
+        <v>0.4763</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9264</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8529</v>
+        <v>2.2234</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4559</v>
+        <v>0.8524</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2014</v>
+        <v>-0.1573</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6573</v>
+        <v>1.0097</v>
       </c>
       <c r="V4" t="n">
-        <v>6.2943</v>
+        <v>1.5733</v>
       </c>
       <c r="W4" t="n">
-        <v>6.2943</v>
+        <v>2.8321</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8238</v>
+        <v>2.8474</v>
       </c>
       <c r="E5" t="n">
-        <v>2.147</v>
+        <v>2.0276</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6768</v>
+        <v>0.8198</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3893</v>
+        <v>2.1936</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0758</v>
+        <v>-1.8123</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6865</v>
+        <v>4.0059</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3374</v>
+        <v>3.1421</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8244</v>
+        <v>-0.1033</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.487</v>
+        <v>3.2454</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-1.709</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1996</v>
+        <v>0.7604</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1117</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0382</v>
+        <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7669</v>
+        <v>0.2832</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9213</v>
+        <v>-0.0028</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8456</v>
+        <v>0.286</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>S. KALLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.791</v>
+        <v>2.12</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2667</v>
+        <v>1.1106</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5243</v>
+        <v>1.0094</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1936</v>
+        <v>0.9009</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8123</v>
+        <v>0.2878</v>
       </c>
       <c r="I6" t="n">
-        <v>4.0059</v>
+        <v>0.613</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1421</v>
+        <v>1.4196</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1033</v>
+        <v>1.1293</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2454</v>
+        <v>0.2903</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9485</v>
+        <v>-0.5187</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.709</v>
+        <v>-0.8414</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7604</v>
+        <v>0.3227</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1117</v>
+        <v>-0.1853</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4823</v>
+        <v>1.297</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2268</v>
+        <v>0.7368</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2363</v>
+        <v>-0.1237</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0095</v>
+        <v>0.8605</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. KALLE</t>
+          <t>H. SANTOS PARRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4284</v>
+        <v>1.5752</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4683</v>
+        <v>-0.1008</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9602000000000001</v>
+        <v>1.676</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9009</v>
+        <v>-0.155</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2878</v>
+        <v>0.2182</v>
       </c>
       <c r="I8" t="n">
-        <v>0.613</v>
+        <v>-0.3732</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4196</v>
+        <v>0.8487</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1293</v>
+        <v>1.46</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2903</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5187</v>
+        <v>-1.0037</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8414</v>
+        <v>-1.2418</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3227</v>
+        <v>0.2381</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0453</v>
+        <v>0.0441</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.766</v>
+        <v>-0.023</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8113</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6294</v>
+        <v>0.945</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6294</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. SANTOS PARRA</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1277</v>
+        <v>1.5118</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3513</v>
+        <v>1.0813</v>
       </c>
       <c r="F9" t="n">
-        <v>1.479</v>
+        <v>0.4306</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.155</v>
+        <v>0.3893</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2182</v>
+        <v>1.0758</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3732</v>
+        <v>-0.6865</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8487</v>
+        <v>1.3374</v>
       </c>
       <c r="K9" t="n">
-        <v>1.46</v>
+        <v>1.8244</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.487</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0037</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2418</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2381</v>
+        <v>-0.1996</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4034</v>
+        <v>1.4549</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2736</v>
+        <v>0.8556</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1298</v>
+        <v>0.5994</v>
       </c>
       <c r="V9" t="n">
-        <v>0.945</v>
+        <v>-1.2589</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.945</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1597</v>
+        <v>0.3376</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4901</v>
+        <v>0.5448</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3303</v>
+        <v>-0.2072</v>
       </c>
       <c r="G10" t="n">
         <v>0.1871</v>
@@ -1234,13 +1234,13 @@
         <v>0.1853</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2126</v>
+        <v>-0.0348</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1641</v>
+        <v>-0.1094</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. GALIANO AVILA</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6191</v>
+        <v>0.0696</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9165</v>
+        <v>-1.9411</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2974</v>
+        <v>2.0107</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9597</v>
+        <v>-2.7194</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2993</v>
+        <v>-2.3154</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3396</v>
+        <v>-0.404</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4035</v>
+        <v>-2.2095</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2791</v>
+        <v>-1.7439</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1244</v>
+        <v>-0.4656</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3633</v>
+        <v>-0.51</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5784</v>
+        <v>-0.5715</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2152</v>
+        <v>0.0616</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6676</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.7057</v>
+        <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0632</v>
+        <v>0.5863</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1269</v>
+        <v>-0.0814</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9364</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>0.945</v>
+        <v>2.2027</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2589</v>
+        <v>2.2027</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6543</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2464</v>
+        <v>-2.1368</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5921</v>
+        <v>1.4821</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7194</v>
+        <v>-1.7589</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3154</v>
+        <v>-0.6621</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.404</v>
+        <v>-1.0967</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2095</v>
+        <v>-1.6926</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7439</v>
+        <v>-0.5113</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4656</v>
+        <v>-1.1813</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.51</v>
+        <v>-0.0663</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5715</v>
+        <v>-0.1508</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0616</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8529</v>
+        <v>-1.1117</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8529</v>
+        <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1375</v>
+        <v>0.1041</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3867</v>
+        <v>-0.2764</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2492</v>
+        <v>0.3805</v>
       </c>
       <c r="V12" t="n">
-        <v>2.2027</v>
+        <v>0.6294</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2027</v>
+        <v>0.9439</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>S. GALIANO AVILA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9966</v>
+        <v>-0.7307</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6265</v>
+        <v>-1.905</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6298</v>
+        <v>1.1743</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7589</v>
+        <v>-0.9597</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6621</v>
+        <v>-1.2993</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0967</v>
+        <v>0.3396</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6926</v>
+        <v>0.4035</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5113</v>
+        <v>0.2791</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1813</v>
+        <v>0.1244</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0663</v>
+        <v>-1.3633</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1508</v>
+        <v>-1.5784</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.2152</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3706</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1117</v>
+        <v>-3.7057</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4823</v>
+        <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2378</v>
+        <v>0.9516</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.766</v>
+        <v>0.1384</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5282</v>
+        <v>0.8133</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6294</v>
+        <v>0.945</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9439</v>
+        <v>1.2589</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3144</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>31.8218</v>
+        <v>32.64260000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>18.2727</v>
+        <v>19.0933</v>
       </c>
       <c r="F14" t="n">
-        <v>13.5493</v>
+        <v>13.5494</v>
       </c>
       <c r="G14" t="n">
-        <v>8.873599999999998</v>
+        <v>8.8736</v>
       </c>
       <c r="H14" t="n">
         <v>-2.147199999999999</v>
@@ -1546,13 +1546,13 @@
         <v>19.4553</v>
       </c>
       <c r="S14" t="n">
-        <v>6.653</v>
+        <v>7.4734</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3727000000000001</v>
+        <v>0.4479</v>
       </c>
       <c r="U14" t="n">
-        <v>7.025799999999999</v>
+        <v>7.0258</v>
       </c>
       <c r="V14" t="n">
         <v>12.5897</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.243</v>
+        <v>2.8145</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4953</v>
+        <v>2.887</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2523</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>2.4287</v>
@@ -1624,13 +1624,13 @@
         <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1672</v>
+        <v>-0.5956</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2037</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0365</v>
+        <v>0.2164</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3155</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6616</v>
+        <v>-0.1216</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5655</v>
+        <v>-0.2717</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0961</v>
+        <v>0.1501</v>
       </c>
       <c r="G17" t="n">
         <v>0.669</v>
@@ -1780,13 +1780,13 @@
         <v>0.3706</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.2347</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8207</v>
+        <v>-0.5269</v>
       </c>
       <c r="U17" t="n">
-        <v>0.046</v>
+        <v>0.2922</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2013</v>
+        <v>-1.5689</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7778</v>
+        <v>-1.0716</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4235</v>
+        <v>-0.4974</v>
       </c>
       <c r="G18" t="n">
         <v>0.8691</v>
@@ -1858,13 +1858,13 @@
         <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3002</v>
+        <v>-0.0675</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2151</v>
+        <v>-0.0786</v>
       </c>
       <c r="U18" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0112</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2589</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VAZQUEZ SUAREZ</t>
+          <t>D. MORILLO LEON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5059</v>
+        <v>-1.5968</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0703</v>
+        <v>-1.6476</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4356</v>
+        <v>0.0508</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5732</v>
+        <v>-1.2968</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4921</v>
+        <v>-0.4904</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0811</v>
+        <v>-0.8064</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1933</v>
+        <v>-0.5455</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0689</v>
+        <v>0.1074</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1244</v>
+        <v>-0.6529</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7665</v>
+        <v>-0.7513</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.561</v>
+        <v>-0.5977</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2056</v>
+        <v>-0.1536</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1117</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.297</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4087</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1</v>
+        <v>0.0706</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.281</v>
+        <v>-0.1756</v>
       </c>
       <c r="U19" t="n">
-        <v>0.181</v>
+        <v>0.2462</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9444</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MORILLO LEON</t>
+          <t>J. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6455</v>
+        <v>-1.7403</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7455</v>
+        <v>-0.9678</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1</v>
+        <v>-0.7726</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2968</v>
+        <v>-0.4326</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4904</v>
+        <v>-0.5525</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8064</v>
+        <v>0.1199</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5455</v>
+        <v>1.5597</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1074</v>
+        <v>0.8025</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6529</v>
+        <v>0.7572</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7513</v>
+        <v>-1.9922</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5977</v>
+        <v>-1.355</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1536</v>
+        <v>-0.6373</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3706</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>-2.4087</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.2234</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0219</v>
+        <v>-1.4369</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2736</v>
+        <v>-1.0626</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2955</v>
+        <v>-0.3743</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>J. VAZQUEZ SUAREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6885</v>
+        <v>-1.9142</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4408</v>
+        <v>-0.5599</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7523</v>
+        <v>-1.3543</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.194</v>
+        <v>-1.5732</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0819</v>
+        <v>-0.4921</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1121</v>
+        <v>-1.0811</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4873</v>
+        <v>1.1933</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1241</v>
+        <v>1.0689</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.1244</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2933</v>
+        <v>-2.7665</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.206</v>
+        <v>-1.561</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4993</v>
+        <v>-1.2056</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.297</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9264</v>
+        <v>2.4087</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1343</v>
+        <v>-0.5083</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6566</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7909</v>
+        <v>0.2624</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2583</v>
+        <v>-0.9444</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2583</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. BRAVO ORTEGA</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2391</v>
+        <v>-2.181</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1636</v>
+        <v>-2.4408</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0755</v>
+        <v>0.2599</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4326</v>
+        <v>-0.194</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5525</v>
+        <v>-0.0819</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1199</v>
+        <v>-0.1121</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5597</v>
+        <v>-0.4873</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8025</v>
+        <v>0.1241</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7572</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9922</v>
+        <v>0.2933</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.355</v>
+        <v>-0.206</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6373</v>
+        <v>0.4993</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4087</v>
+        <v>-1.297</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2234</v>
+        <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9357</v>
+        <v>-0.3581</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2584</v>
+        <v>-0.6566</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6772</v>
+        <v>0.2984</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3144</v>
+        <v>-1.2583</v>
       </c>
       <c r="W22" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6294</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1076</v>
+        <v>-2.8619</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1636</v>
+        <v>0.2616</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2712</v>
+        <v>-3.1235</v>
       </c>
       <c r="G23" t="n">
         <v>0.7181</v>
@@ -2248,13 +2248,13 @@
         <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1227</v>
+        <v>-0.877</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4924</v>
+        <v>-0.3945</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6302</v>
+        <v>-0.4825</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5177</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7464</v>
+        <v>-3.9187</v>
       </c>
       <c r="E24" t="n">
         <v>-2.5395</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2069</v>
+        <v>-1.3792</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6103</v>
@@ -2326,13 +2326,13 @@
         <v>1.1117</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2345</v>
+        <v>0.0622</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2226</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4571</v>
+        <v>0.2848</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2589</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5514</v>
+        <v>-4.4454</v>
       </c>
       <c r="E25" t="n">
         <v>-0.3221</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.2293</v>
+        <v>-4.1233</v>
       </c>
       <c r="G25" t="n">
         <v>-2.147</v>
@@ -2404,13 +2404,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.6516</v>
       </c>
       <c r="T25" t="n">
         <v>-0.4924</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2651</v>
+        <v>-0.1592</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2027</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.691</v>
+        <v>-5.9356</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.3749</v>
+        <v>-1.6687</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.3161</v>
+        <v>-4.2669</v>
       </c>
       <c r="G26" t="n">
         <v>-1.635</v>
@@ -2482,13 +2482,13 @@
         <v>1.297</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6113</v>
+        <v>-0.8559</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6603</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>0.049</v>
+        <v>0.0982</v>
       </c>
       <c r="V26" t="n">
         <v>-2.5183</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-8.6707</v>
+        <v>-8.3431</v>
       </c>
       <c r="E27" t="n">
         <v>-5.852</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.8186</v>
+        <v>-2.4911</v>
       </c>
       <c r="G27" t="n">
         <v>-5.3137</v>
@@ -2560,13 +2560,13 @@
         <v>2.2234</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.8747</v>
+        <v>-0.5471</v>
       </c>
       <c r="T27" t="n">
         <v>-0.8792</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0045</v>
+        <v>0.332</v>
       </c>
       <c r="V27" t="n">
         <v>-0.6294</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-31.8219</v>
+        <v>-31.1689</v>
       </c>
       <c r="E28" t="n">
         <v>-13.549</v>
       </c>
       <c r="F28" t="n">
-        <v>-18.2728</v>
+        <v>-17.6199</v>
       </c>
       <c r="G28" t="n">
         <v>-8.8736</v>
@@ -2638,13 +2638,13 @@
         <v>15.7492</v>
       </c>
       <c r="S28" t="n">
-        <v>-6.653</v>
+        <v>-5.999900000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>-7.0258</v>
+        <v>-7.025799999999999</v>
       </c>
       <c r="U28" t="n">
-        <v>0.373</v>
+        <v>1.0258</v>
       </c>
       <c r="V28" t="n">
         <v>-12.5897</v>
